--- a/predictionPlan.xlsx
+++ b/predictionPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taekoharada/Documents/myProject/capstone/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41897322-5116-0047-B815-3324703E7EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B994F3CB-9F17-2846-A4AE-9BD76B85E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{9D2222F7-D692-7248-B611-4899D4DDFAF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Order data</t>
   </si>
@@ -72,6 +72,18 @@
   </si>
   <si>
     <t>df_dummy_data['月'] = df_dummy_data['月'].astype(int)</t>
+  </si>
+  <si>
+    <t>df_encoded = pd.get_dummies(df_dummy_data, columns=['家具カテゴリ'], drop_first=True)</t>
+  </si>
+  <si>
+    <t>4. 移動平均の計算</t>
+  </si>
+  <si>
+    <t>Range of last 3 months</t>
+  </si>
+  <si>
+    <t>df_dummy_data['移動平均'] = df_dummy_data['注文数'].rolling(window=3).mean()</t>
   </si>
 </sst>
 </file>
@@ -451,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BD081D-D88F-C44A-A4E4-D01C9CAE5B0D}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -548,6 +560,26 @@
         <v>9</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/predictionPlan.xlsx
+++ b/predictionPlan.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taekoharada/Documents/myProject/capstone/python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taekoharada/Documents/myProject/capstone/dataPrediction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B994F3CB-9F17-2846-A4AE-9BD76B85E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B4AFAB-BC83-BD47-8F2A-166AFE06ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{9D2222F7-D692-7248-B611-4899D4DDFAF4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{9D2222F7-D692-7248-B611-4899D4DDFAF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="models" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>Order data</t>
   </si>
@@ -84,6 +85,39 @@
   </si>
   <si>
     <t>df_dummy_data['移動平均'] = df_dummy_data['注文数'].rolling(window=3).mean()</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Suitable for</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Linear Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Random Forest Regressor</t>
+  </si>
+  <si>
+    <t>Gradient Boosting Regressor</t>
+  </si>
+  <si>
+    <t>K-Neighbors Regressor</t>
+  </si>
+  <si>
+    <t>Support Vector Regressor</t>
+  </si>
+  <si>
+    <t>Good/Bad</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Bad</t>
   </si>
 </sst>
 </file>
@@ -126,9 +160,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,4 +623,73 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFFF6DE-4351-A147-98B6-2E204A1664C1}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="56" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="56" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>